--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_atacama.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:23</t>
+    <t xml:space="preserve">2026-09-24 01:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -561,7 +561,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>9</v>
@@ -570,7 +570,7 @@
         <v>-0.15</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>-0.37</v>
@@ -590,10 +590,10 @@
         <v>9</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>-0.42</v>
@@ -616,7 +616,7 @@
         <v>-0.05</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>-0.57</v>
@@ -630,7 +630,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>9</v>
@@ -639,7 +639,7 @@
         <v>0.22</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0.61</v>
@@ -662,10 +662,10 @@
         <v>0.26</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="7">
@@ -682,10 +682,10 @@
         <v>9</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0.33</v>
@@ -705,10 +705,10 @@
         <v>9</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>-0.28</v>
@@ -728,10 +728,10 @@
         <v>9</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>-0.22</v>
@@ -751,13 +751,13 @@
         <v>7</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="11">
@@ -774,13 +774,13 @@
         <v>7</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="12">
@@ -791,16 +791,16 @@
         <v>14</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0.01</v>
@@ -814,19 +814,19 @@
         <v>14</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.39</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="14">
@@ -837,19 +837,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.69</v>
+        <v>0.71</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="15">
@@ -860,19 +860,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="16">
@@ -889,13 +889,13 @@
         <v>9</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="17">
@@ -912,13 +912,13 @@
         <v>9</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="18">
@@ -938,7 +938,7 @@
         <v>-0.41</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>-0.38</v>
@@ -961,7 +961,7 @@
         <v>-0.2</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>-0.06</v>
@@ -981,10 +981,10 @@
         <v>9</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>-0.24</v>
@@ -1007,7 +1007,7 @@
         <v>0.06</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0.38</v>
@@ -1027,13 +1027,13 @@
         <v>9</v>
       </c>
       <c r="E22" s="2" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>346</v>
+      </c>
+      <c r="G22" s="2" t="n">
         <v>-0.11</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>343</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>-0.12</v>
       </c>
     </row>
     <row r="23">
@@ -1050,13 +1050,13 @@
         <v>9</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_atacama.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:13</t>
+    <t xml:space="preserve">2026-10-01 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_atacama.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:08</t>
+    <t xml:space="preserve">2026-10-05 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
